--- a/export_templates/warehouse_checksheet.xlsx
+++ b/export_templates/warehouse_checksheet.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://salesbridge-my.sharepoint.com/personal/kantapon_arunrungruengkit_bridgestone_com/Documents/Desktop/gogdun/03 Audit/SMA-WH/02 Checksheet/"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="30" documentId="8_{2020F24C-AC5C-4112-94EC-222E48E18D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F1CA6DC-29FC-4232-8A92-4A5C3EB09025}"/>
   <bookViews>
